--- a/spec_crews/datadog_monitoring_v3.xlsx
+++ b/spec_crews/datadog_monitoring_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jochungi/WORK/DEV/meta_ai_generator/spec_crews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE05470-8054-4347-A8B7-A54822AA75DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A508C606-DF1C-7843-95A9-83264004602A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
   <si>
     <t>task_name</t>
   </si>
@@ -348,6 +348,18 @@
   <si>
     <t>Datadog Logs API를 사용하여 {time_range} 시간 범위 동안 {datadog_query} 쿼리와 일치하는 애플리케이션 로그를 가져옵니다. 최대 {limit}개의 로그 이벤트를 가져옵니다. 반환된 데이터에 타임스탬프, 로그 레벨, 메시지, 서비스 이름 및 스택 트레이스가 포함되도록 합니다.  Datadog 로그 검색 API 요청을 아래와 같이 구성합니다.  조회 옵션(search_option) 은 {search_option} 이고,  여기에 맞게 Tool 을 호출합니다. 데이터 0건 시 임의 생성 금지 및 "조회 결과 없음" 을 분명히 명시합니다.  
 - 예외사항 :  hostname_mismatch issue 는 오류가 아님으로 정상으로 간주하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mcp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>search_datadog_logs,search_datadog_apm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>send_outlook_mail</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -409,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,6 +437,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,7 +485,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -517,6 +535,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -858,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -871,9 +895,10 @@
     <col min="8" max="8" width="29.85546875" customWidth="1"/>
     <col min="9" max="9" width="38.28515625" customWidth="1"/>
     <col min="10" max="11" width="19.28515625" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -901,14 +926,17 @@
       <c r="I1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="199" customHeight="1">
+    <row r="2" spans="1:12" ht="199" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,11 +961,13 @@
         <v>16</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:11" ht="164" customHeight="1">
+    <row r="3" spans="1:12" ht="164" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -966,7 +996,7 @@
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="203" customHeight="1">
+    <row r="4" spans="1:12" ht="203" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -997,7 +1027,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="131" customHeight="1">
+    <row r="5" spans="1:12" ht="131" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -1024,9 +1054,11 @@
         <v>25</v>
       </c>
       <c r="J5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
